--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129850336</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>96374</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572660</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587856</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129848066</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,22 +820,26 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572716</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6588058</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,22 +898,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129852135</v>
+        <v>129848357</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,24 +921,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -940,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572573</v>
+        <v>572691</v>
       </c>
       <c r="R4" t="n">
-        <v>6587903</v>
+        <v>6587977</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -985,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,44 +1018,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129849269</v>
+        <v>129852516</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>92052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572574</v>
       </c>
       <c r="R5" t="n">
-        <v>6587913</v>
+        <v>6587839</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853662</v>
+        <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>5177</v>
+        <v>96376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,32 +1160,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572512</v>
+        <v>572568</v>
       </c>
       <c r="R6" t="n">
-        <v>6587864</v>
+        <v>6587950</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1210,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,46 +1260,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852861</v>
+        <v>129853663</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1294,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572560</v>
+        <v>572512</v>
       </c>
       <c r="R7" t="n">
-        <v>6587918</v>
+        <v>6587864</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1329,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,47 +1375,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848357</v>
+        <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>92052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1414,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572691</v>
+        <v>572671</v>
       </c>
       <c r="R8" t="n">
-        <v>6587977</v>
+        <v>6587913</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129853663</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,45 +1505,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572512</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587864</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1586,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,68 +1602,81 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129853122</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>96374</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572568</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587950</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,19 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:18</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,45 +1719,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129850330</v>
+        <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>58106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1740,28 +1791,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572647</v>
+        <v>572722</v>
       </c>
       <c r="R11" t="n">
-        <v>6587994</v>
+        <v>6588063</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,7 +1845,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1855,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,50 +1870,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129850374</v>
+        <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>96374</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1866,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572599</v>
+        <v>572538</v>
       </c>
       <c r="R12" t="n">
-        <v>6587880</v>
+        <v>6587829</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -1901,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,55 +1992,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129852516</v>
+        <v>129861976</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572574</v>
+        <v>572626</v>
       </c>
       <c r="R13" t="n">
-        <v>6587839</v>
+        <v>6587871</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2075,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,12 +2085,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,8 +2094,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2057,55 +2138,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129848578</v>
+        <v>129850320</v>
       </c>
       <c r="B14" t="n">
-        <v>92050</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572671</v>
+        <v>572693</v>
       </c>
       <c r="R14" t="n">
-        <v>6587913</v>
+        <v>6588000</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,7 +2217,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2144,12 +2227,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,22 +2242,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129861934</v>
+        <v>129849857</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,17 +2292,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572577</v>
+        <v>572655</v>
       </c>
       <c r="R15" t="n">
-        <v>6587848</v>
+        <v>6587890</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,14 +2329,19 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,34 +2350,8 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2311,10 +2368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129863852</v>
+        <v>129853667</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2322,49 +2379,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>572538</v>
       </c>
       <c r="R16" t="n">
-        <v>6587894</v>
+        <v>6587829</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,12 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,53 +2467,43 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129847959</v>
+        <v>129853671</v>
       </c>
       <c r="B17" t="n">
-        <v>58106</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2482,23 +2520,27 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572722</v>
+        <v>572561</v>
       </c>
       <c r="R17" t="n">
-        <v>6588063</v>
+        <v>6587819</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2527,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,7 +2579,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2564,37 +2611,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853669</v>
+        <v>129850334</v>
       </c>
       <c r="B18" t="n">
-        <v>91597</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2602,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572538</v>
+        <v>572673</v>
       </c>
       <c r="R18" t="n">
-        <v>6587829</v>
+        <v>6587920</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2637,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2647,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129861976</v>
+        <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>5177</v>
+        <v>96376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,50 +2738,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572626</v>
+        <v>572660</v>
       </c>
       <c r="R19" t="n">
-        <v>6587871</v>
+        <v>6587856</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2757,7 +2801,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2767,7 +2811,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,87 +2820,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129850320</v>
+        <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2864,13 +2876,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572693</v>
+        <v>572716</v>
       </c>
       <c r="R20" t="n">
-        <v>6588000</v>
+        <v>6588058</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2899,7 +2911,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2909,7 +2921,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,10 +2948,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129850334</v>
+        <v>129853662</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2947,21 +2959,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2980,10 +2992,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572673</v>
+        <v>572512</v>
       </c>
       <c r="R21" t="n">
-        <v>6587920</v>
+        <v>6587864</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3015,7 +3027,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3025,7 +3037,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3052,41 +3064,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129849857</v>
+        <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3094,13 +3111,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572655</v>
+        <v>572560</v>
       </c>
       <c r="R22" t="n">
-        <v>6587890</v>
+        <v>6587918</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3129,7 +3146,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3139,7 +3156,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3154,69 +3171,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129848027</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>5177</v>
+        <v>57733</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572720</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6588056</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3245,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3255,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129853667</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>96376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3325,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572538</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587829</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3360,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,61 +3409,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129853671</v>
+        <v>129848027</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>5177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572561</v>
+        <v>572720</v>
       </c>
       <c r="R25" t="n">
-        <v>6587819</v>
+        <v>6588056</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3483,7 +3488,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3493,12 +3498,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3513,12 +3513,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,35 +1505,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,24 +1569,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1597,21 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,30 +1640,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,14 +1709,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,21 +1746,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129849857</v>
+        <v>129853667</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,30 +2265,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2296,13 +2297,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572655</v>
+        <v>572538</v>
       </c>
       <c r="R15" t="n">
-        <v>6587890</v>
+        <v>6587829</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,19 +2357,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853667</v>
+        <v>129853671</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2396,28 +2397,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572538</v>
+        <v>572561</v>
       </c>
       <c r="R16" t="n">
-        <v>6587829</v>
+        <v>6587819</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2446,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2456,7 +2465,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,76 +2485,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853671</v>
+        <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572561</v>
+        <v>572673</v>
       </c>
       <c r="R17" t="n">
-        <v>6587819</v>
+        <v>6587920</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,12 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,55 +2601,53 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129850334</v>
+        <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572673</v>
+        <v>572655</v>
       </c>
       <c r="R18" t="n">
-        <v>6587920</v>
+        <v>6587890</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3523,6 +3523,2908 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129880266</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>572635</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6588012</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Växer grov rötad tallåga</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129880787</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5469</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>572432</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6587788</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kläckhål i björklåga</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129881338</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>572461</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6587873</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129881229</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>572425</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6587873</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129881456</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>572594</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6587833</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer i sluttning ner mot mosse.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129879688</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>572642</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6587983</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129880591</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>572591</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6587910</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stor förekomst på tallåga i sumpig skogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129881407</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91836</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gropticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Postia guttulata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>572508</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6587870</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129881108</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>572440</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6587862</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Vidväxt på granlåga</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129880315</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96376</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>572590</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6587967</v>
+      </c>
+      <c r="S35" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kudde 30 cm hög</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129878905</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>572680</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6588009</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Växer på rötad tallåga</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129881042</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>572434</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6587846</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Växer på granlåga i blockrik terräng vid hällmark</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129880860</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>572415</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6587791</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gnagspår på gammal tall i hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129880273</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>572598</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6587998</v>
+      </c>
+      <c r="S39" t="n">
+        <v>7</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Växer på granlåga i sumpskogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129881486</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>572603</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6587829</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129879675</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>572661</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6588006</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129881633</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>572736</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6587886</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Över hundra plantor på ett stenblock. Mossrik och  Fuktig skogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129880712</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>572458</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6587778</v>
+      </c>
+      <c r="S43" t="n">
+        <v>7</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129880838</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>572431</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6587805</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på tall i hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129881468</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>572602</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6587826</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Växer i mossan bland grov gran nära en mosse</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129880167</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>572644</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6588032</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Växer på tallåga</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129880352</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>572564</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6587969</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129879841</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90981</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>572640</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6588022</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129880557</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97062</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>572578</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6587934</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i fuktig skogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -3641,65 +3641,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129880787</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>5469</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572432</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3728,7 +3718,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3738,12 +3728,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3770,55 +3760,65 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881338</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572461</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3889,41 +3889,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3931,10 +3936,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3966,7 +3971,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3976,12 +3981,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4008,46 +4013,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129881456</v>
+        <v>129881229</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572594</v>
+        <v>572425</v>
       </c>
       <c r="R30" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853667</v>
+        <v>129849857</v>
       </c>
       <c r="B15" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,31 +2265,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,13 +2296,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572538</v>
+        <v>572655</v>
       </c>
       <c r="R15" t="n">
-        <v>6587829</v>
+        <v>6587890</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2341,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,19 +2356,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853671</v>
+        <v>129853667</v>
       </c>
       <c r="B16" t="n">
         <v>57733</v>
@@ -2397,36 +2396,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572561</v>
+        <v>572538</v>
       </c>
       <c r="R16" t="n">
-        <v>6587819</v>
+        <v>6587829</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,69 +2471,76 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2579,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,53 +2599,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129849857</v>
+        <v>129850334</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572655</v>
+        <v>572673</v>
       </c>
       <c r="R18" t="n">
-        <v>6587890</v>
+        <v>6587920</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3641,55 +3641,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881338</v>
+        <v>129880787</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>5469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572461</v>
+        <v>572432</v>
       </c>
       <c r="R27" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3718,7 +3728,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3728,12 +3738,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,65 +3770,55 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129880787</v>
+        <v>129881338</v>
       </c>
       <c r="B28" t="n">
-        <v>5469</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572432</v>
+        <v>572461</v>
       </c>
       <c r="R28" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3889,46 +3889,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881456</v>
+        <v>129881229</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3936,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572594</v>
+        <v>572425</v>
       </c>
       <c r="R29" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3971,7 +3966,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3981,12 +3976,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4013,41 +4008,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R30" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -1152,7 +1152,7 @@
         <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,30 +1505,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,14 +1574,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,21 +1611,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,35 +1639,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,24 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,6 +1719,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,6 +1731,21 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2254,41 +2254,43 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129849857</v>
+        <v>129850334</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>8450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2296,13 +2298,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572655</v>
+        <v>572673</v>
       </c>
       <c r="R15" t="n">
-        <v>6587890</v>
+        <v>6587920</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,22 +2358,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853667</v>
+        <v>129849857</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,31 +2381,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2411,13 +2412,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572538</v>
+        <v>572655</v>
       </c>
       <c r="R16" t="n">
-        <v>6587829</v>
+        <v>6587890</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2446,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2456,7 +2457,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,19 +2472,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853671</v>
+        <v>129853667</v>
       </c>
       <c r="B17" t="n">
         <v>57733</v>
@@ -2511,36 +2512,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572561</v>
+        <v>572538</v>
       </c>
       <c r="R17" t="n">
-        <v>6587819</v>
+        <v>6587829</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,12 +2572,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,69 +2587,76 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R18" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2695,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96376</v>
+        <v>96386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57733</v>
+        <v>96386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96376</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,49 +3525,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129880266</v>
+        <v>129881229</v>
       </c>
       <c r="B26" t="n">
-        <v>97062</v>
+        <v>91599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572635</v>
+        <v>572425</v>
       </c>
       <c r="R26" t="n">
-        <v>6588012</v>
+        <v>6587873</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3599,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3609,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer grov rötad tallåga</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,65 +3644,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129880787</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>5469</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572432</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3728,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3738,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3770,41 +3763,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881338</v>
+        <v>129881456</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3812,13 +3810,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572461</v>
+        <v>572594</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3857,12 +3855,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3889,52 +3887,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881229</v>
+        <v>129880787</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>5469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572425</v>
+        <v>572432</v>
       </c>
       <c r="R29" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3966,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3976,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4008,44 +4016,36 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129881456</v>
+        <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>97072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572594</v>
+        <v>572591</v>
       </c>
       <c r="R30" t="n">
-        <v>6587833</v>
+        <v>6587910</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Stor förekomst på tallåga i sumpig skogsmiljö</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,38 +4248,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129880591</v>
+        <v>129881108</v>
       </c>
       <c r="B32" t="n">
-        <v>97062</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4287,10 +4290,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572591</v>
+        <v>572440</v>
       </c>
       <c r="R32" t="n">
-        <v>6587910</v>
+        <v>6587862</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4322,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4332,12 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Stor förekomst på tallåga i sumpig skogsmiljö</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4364,41 +4367,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B33" t="n">
-        <v>91836</v>
+        <v>96386</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4406,13 +4406,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R33" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4483,10 +4483,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129881108</v>
+        <v>129881407</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>91836</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4494,21 +4494,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572440</v>
+        <v>572508</v>
       </c>
       <c r="R34" t="n">
-        <v>6587862</v>
+        <v>6587870</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129880315</v>
+        <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>96376</v>
+        <v>97072</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,17 +4637,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572590</v>
+        <v>572680</v>
       </c>
       <c r="R35" t="n">
-        <v>6587967</v>
+        <v>6588009</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Växer på rötad tallåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4718,49 +4718,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129878905</v>
+        <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>97062</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572680</v>
+        <v>572434</v>
       </c>
       <c r="R36" t="n">
-        <v>6588009</v>
+        <v>6587846</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4792,7 +4795,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4802,12 +4805,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer på rötad tallåga</t>
+          <t>Växer på granlåga i blockrik terräng vid hällmark</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4834,52 +4837,62 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129881042</v>
+        <v>129880860</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572434</v>
+        <v>572415</v>
       </c>
       <c r="R37" t="n">
-        <v>6587846</v>
+        <v>6587791</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4911,7 +4924,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4921,12 +4934,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer på granlåga i blockrik terräng vid hällmark</t>
+          <t>Gnagspår på gammal tall i hällmarksskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4953,65 +4966,55 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129880860</v>
+        <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>91599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572415</v>
+        <v>572598</v>
       </c>
       <c r="R38" t="n">
-        <v>6587791</v>
+        <v>6587998</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5040,7 +5043,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5050,12 +5053,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gnagspår på gammal tall i hällmarksskog</t>
+          <t>Växer på granlåga i sumpskogsmiljö</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5082,55 +5085,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129880273</v>
+        <v>129881486</v>
       </c>
       <c r="B39" t="n">
-        <v>91599</v>
+        <v>5177</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572598</v>
+        <v>572603</v>
       </c>
       <c r="R39" t="n">
-        <v>6587998</v>
+        <v>6587829</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5159,7 +5172,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5169,12 +5182,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Växer på granlåga i sumpskogsmiljö</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5201,32 +5209,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129881486</v>
+        <v>129879675</v>
       </c>
       <c r="B40" t="n">
-        <v>5177</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5234,12 +5242,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5249,17 +5256,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572603</v>
+        <v>572661</v>
       </c>
       <c r="R40" t="n">
-        <v>6587829</v>
+        <v>6588006</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5288,7 +5295,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5298,7 +5305,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5325,10 +5337,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129879675</v>
+        <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5336,21 +5348,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5362,7 +5374,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5372,17 +5384,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572661</v>
+        <v>572458</v>
       </c>
       <c r="R41" t="n">
-        <v>6588006</v>
+        <v>6587778</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5411,7 +5423,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5421,12 +5433,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på tall</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5453,60 +5460,64 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129881633</v>
+        <v>129880838</v>
       </c>
       <c r="B42" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572736</v>
+        <v>572431</v>
       </c>
       <c r="R42" t="n">
-        <v>6587886</v>
+        <v>6587805</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5535,7 +5546,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5545,12 +5556,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Över hundra plantor på ett stenblock. Mossrik och  Fuktig skogsmiljö</t>
+          <t>Färska hackmärken på tall i hällmarksskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5577,64 +5588,60 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129880712</v>
+        <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>57896</v>
+        <v>98790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572458</v>
+        <v>572602</v>
       </c>
       <c r="R43" t="n">
-        <v>6587778</v>
+        <v>6587826</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5663,7 +5670,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5673,7 +5680,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Växer i mossan bland grov gran nära en mosse</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5700,32 +5712,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129880838</v>
+        <v>129880352</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>5177</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5733,11 +5745,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5751,13 +5764,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572431</v>
+        <v>572564</v>
       </c>
       <c r="R44" t="n">
-        <v>6587805</v>
+        <v>6587969</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5786,7 +5799,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5796,12 +5809,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på tall i hällmarksskog</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5828,44 +5836,36 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129881468</v>
+        <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>98780</v>
+        <v>97072</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5875,13 +5875,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572602</v>
+        <v>572578</v>
       </c>
       <c r="R45" t="n">
-        <v>6587826</v>
+        <v>6587934</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Växer i mossan bland grov gran nära en mosse</t>
+          <t>Växer på tallåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5952,10 +5952,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129880167</v>
+        <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572644</v>
+        <v>572635</v>
       </c>
       <c r="R46" t="n">
-        <v>6588032</v>
+        <v>6588012</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer på tallåga</t>
+          <t>Växer grov rötad tallåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6068,65 +6068,60 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129880352</v>
+        <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>5177</v>
+        <v>98790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572564</v>
+        <v>572736</v>
       </c>
       <c r="R47" t="n">
-        <v>6587969</v>
+        <v>6587886</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6155,7 +6150,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6165,7 +6160,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Över hundra plantor på ett stenblock. Mossrik och  Fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6185,17 +6185,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Via Michael Lander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129879841</v>
+        <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>90981</v>
+        <v>97072</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6203,30 +6203,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5685</v>
+        <v>2590</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6234,10 +6231,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572640</v>
+        <v>572644</v>
       </c>
       <c r="R48" t="n">
-        <v>6588022</v>
+        <v>6588032</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6269,7 +6266,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6279,12 +6276,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Växer på tallåga i äldre barrblandskog</t>
+          <t>Växer på tallåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6311,10 +6308,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129880557</v>
+        <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>97062</v>
+        <v>90981</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6322,41 +6319,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2590</v>
+        <v>5685</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572578</v>
+        <v>572640</v>
       </c>
       <c r="R49" t="n">
-        <v>6587934</v>
+        <v>6588022</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Växer på tallåga i fuktig skogsmiljö</t>
+          <t>Växer på tallåga i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129848578</v>
       </c>
       <c r="B5" t="n">
         <v>92052</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587913</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,38 +1149,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129852516</v>
       </c>
       <c r="B6" t="n">
-        <v>96386</v>
+        <v>92052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572574</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587839</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,54 +1256,50 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129853122</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>96386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572568</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587950</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1338,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,41 +1379,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129853663</v>
       </c>
       <c r="B8" t="n">
-        <v>92052</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572512</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587864</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,35 +1505,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,24 +1569,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1597,21 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,30 +1640,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,14 +1709,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,21 +1746,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129881108</v>
+        <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>91836</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572440</v>
+        <v>572508</v>
       </c>
       <c r="R32" t="n">
-        <v>6587862</v>
+        <v>6587870</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,38 +4367,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129880315</v>
+        <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>96386</v>
+        <v>91599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4406,13 +4409,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572590</v>
+        <v>572440</v>
       </c>
       <c r="R33" t="n">
-        <v>6587967</v>
+        <v>6587862</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4451,12 +4454,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4483,41 +4486,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>91836</v>
+        <v>96386</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R34" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         <v>129848578</v>
       </c>
       <c r="B5" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,41 +1149,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129852516</v>
+        <v>129853663</v>
       </c>
       <c r="B6" t="n">
-        <v>92052</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1192,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572574</v>
+        <v>572512</v>
       </c>
       <c r="R6" t="n">
-        <v>6587839</v>
+        <v>6587864</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,50 +1252,53 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853122</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>96386</v>
+        <v>92055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,13 +1306,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572568</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587950</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1351,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,54 +1371,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853663</v>
+        <v>129853122</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>96390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572512</v>
+        <v>572568</v>
       </c>
       <c r="R8" t="n">
-        <v>6587864</v>
+        <v>6587950</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,7 +1497,7 @@
         <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2254,41 +2254,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129850334</v>
+        <v>129853667</v>
       </c>
       <c r="B15" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2298,10 +2297,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572673</v>
+        <v>572538</v>
       </c>
       <c r="R15" t="n">
-        <v>6587920</v>
+        <v>6587829</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2333,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129849857</v>
+        <v>129853671</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,44 +2380,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572655</v>
+        <v>572561</v>
       </c>
       <c r="R16" t="n">
-        <v>6587890</v>
+        <v>6587819</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,7 +2465,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,40 +2497,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853667</v>
+        <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2527,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572538</v>
+        <v>572673</v>
       </c>
       <c r="R17" t="n">
-        <v>6587829</v>
+        <v>6587920</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2562,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2572,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,10 +2613,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853671</v>
+        <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>91602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,53 +2624,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572561</v>
+        <v>572655</v>
       </c>
       <c r="R18" t="n">
-        <v>6587819</v>
+        <v>6587890</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,12 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96386</v>
+        <v>57734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>96390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,52 +3525,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881229</v>
+        <v>129880787</v>
       </c>
       <c r="B26" t="n">
-        <v>91599</v>
+        <v>5469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572425</v>
+        <v>572432</v>
       </c>
       <c r="R26" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3602,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3612,12 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,10 +3654,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3686,13 +3696,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R27" t="n">
         <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3731,12 +3741,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,46 +3773,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881456</v>
+        <v>129881338</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3810,13 +3815,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572594</v>
+        <v>572461</v>
       </c>
       <c r="R28" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,62 +3892,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129880787</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>5469</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572432</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587788</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>91836</v>
+        <v>91839</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>96386</v>
+        <v>96390</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129879675</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129880838</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97072</v>
+        <v>97076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129848578</v>
+        <v>129852516</v>
       </c>
       <c r="B5" t="n">
         <v>92055</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572574</v>
       </c>
       <c r="R5" t="n">
-        <v>6587913</v>
+        <v>6587839</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,42 +1149,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853663</v>
+        <v>129848578</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>92055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,13 +1191,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572512</v>
+        <v>572671</v>
       </c>
       <c r="R6" t="n">
-        <v>6587864</v>
+        <v>6587913</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,53 +1256,50 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852516</v>
+        <v>129853122</v>
       </c>
       <c r="B7" t="n">
-        <v>92055</v>
+        <v>96390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1306,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572574</v>
+        <v>572568</v>
       </c>
       <c r="R7" t="n">
-        <v>6587839</v>
+        <v>6587950</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,12 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,50 +1367,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853122</v>
+        <v>129853663</v>
       </c>
       <c r="B8" t="n">
-        <v>96390</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572568</v>
+        <v>572512</v>
       </c>
       <c r="R8" t="n">
-        <v>6587950</v>
+        <v>6587864</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853667</v>
+        <v>129849857</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,31 +2265,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,13 +2296,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572538</v>
+        <v>572655</v>
       </c>
       <c r="R15" t="n">
-        <v>6587829</v>
+        <v>6587890</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2341,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,19 +2356,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853671</v>
+        <v>129853667</v>
       </c>
       <c r="B16" t="n">
         <v>57734</v>
@@ -2397,36 +2396,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572561</v>
+        <v>572538</v>
       </c>
       <c r="R16" t="n">
-        <v>6587819</v>
+        <v>6587829</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,69 +2471,76 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2579,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,53 +2599,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129849857</v>
+        <v>129850334</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572655</v>
+        <v>572673</v>
       </c>
       <c r="R18" t="n">
-        <v>6587890</v>
+        <v>6587920</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
+        <v>96390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96390</v>
+        <v>57734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3654,41 +3654,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B27" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3696,10 +3701,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R27" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3731,7 +3736,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3741,12 +3746,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3773,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B28" t="n">
         <v>91602</v>
@@ -3815,13 +3820,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R28" t="n">
         <v>6587873</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,12 +3865,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,46 +3897,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881456</v>
+        <v>129881338</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572594</v>
+        <v>572461</v>
       </c>
       <c r="R29" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4248,41 +4248,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B32" t="n">
-        <v>91839</v>
+        <v>96390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4290,13 +4287,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R32" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4325,7 +4322,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4332,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,10 +4364,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881108</v>
+        <v>129881407</v>
       </c>
       <c r="B33" t="n">
-        <v>91602</v>
+        <v>91839</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4378,21 +4375,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4409,10 +4406,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572440</v>
+        <v>572508</v>
       </c>
       <c r="R33" t="n">
-        <v>6587862</v>
+        <v>6587870</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4444,7 +4441,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4454,12 +4451,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4486,38 +4483,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129880315</v>
+        <v>129881108</v>
       </c>
       <c r="B34" t="n">
-        <v>96390</v>
+        <v>91602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572590</v>
+        <v>572440</v>
       </c>
       <c r="R34" t="n">
-        <v>6587967</v>
+        <v>6587862</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,41 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,55 +779,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1149,41 +1149,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129848578</v>
+        <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>96390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1191,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572671</v>
+        <v>572568</v>
       </c>
       <c r="R6" t="n">
-        <v>6587913</v>
+        <v>6587950</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,50 +1248,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853122</v>
+        <v>129853663</v>
       </c>
       <c r="B7" t="n">
-        <v>96390</v>
+        <v>57734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572568</v>
+        <v>572512</v>
       </c>
       <c r="R7" t="n">
-        <v>6587950</v>
+        <v>6587864</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1342,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,42 +1375,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853663</v>
+        <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>92055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572512</v>
+        <v>572671</v>
       </c>
       <c r="R8" t="n">
-        <v>6587864</v>
+        <v>6587913</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,30 +1505,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,14 +1574,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,21 +1611,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,35 +1639,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,24 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,6 +1719,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,6 +1731,21 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129849857</v>
+        <v>129853667</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>57734</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,30 +2265,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2296,13 +2297,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572655</v>
+        <v>572538</v>
       </c>
       <c r="R15" t="n">
-        <v>6587890</v>
+        <v>6587829</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,19 +2357,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853667</v>
+        <v>129853671</v>
       </c>
       <c r="B16" t="n">
         <v>57734</v>
@@ -2396,28 +2397,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572538</v>
+        <v>572561</v>
       </c>
       <c r="R16" t="n">
-        <v>6587829</v>
+        <v>6587819</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2446,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2456,7 +2465,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,76 +2485,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853671</v>
+        <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572561</v>
+        <v>572673</v>
       </c>
       <c r="R17" t="n">
-        <v>6587819</v>
+        <v>6587920</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,12 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,55 +2601,53 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129850334</v>
+        <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>91602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572673</v>
+        <v>572655</v>
       </c>
       <c r="R18" t="n">
-        <v>6587920</v>
+        <v>6587890</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96390</v>
+        <v>57734</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57734</v>
+        <v>96390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,62 +3525,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129880787</v>
+        <v>129881229</v>
       </c>
       <c r="B26" t="n">
-        <v>5469</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572432</v>
+        <v>572425</v>
       </c>
       <c r="R26" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3612,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3654,46 +3644,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881456</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3701,13 +3686,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572594</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3736,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3746,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3778,52 +3763,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881229</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>91602</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572425</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3865,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3897,41 +3892,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881338</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572461</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4248,38 +4248,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129880315</v>
+        <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>96390</v>
+        <v>91839</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4287,13 +4290,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572590</v>
+        <v>572508</v>
       </c>
       <c r="R32" t="n">
-        <v>6587967</v>
+        <v>6587870</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4322,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4332,12 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4364,10 +4367,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881407</v>
+        <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91839</v>
+        <v>91602</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4375,21 +4378,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4406,10 +4409,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572508</v>
+        <v>572440</v>
       </c>
       <c r="R33" t="n">
-        <v>6587870</v>
+        <v>6587862</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4451,12 +4454,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4483,41 +4486,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129881108</v>
+        <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>91602</v>
+        <v>96390</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572440</v>
+        <v>572590</v>
       </c>
       <c r="R34" t="n">
-        <v>6587862</v>
+        <v>6587967</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -913,7 +913,7 @@
         <v>129848357</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,41 +1030,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129853663</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572512</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587864</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1133,53 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129848578</v>
       </c>
       <c r="B6" t="n">
-        <v>96390</v>
+        <v>92058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572671</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587913</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,54 +1252,53 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>92058</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1306,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1351,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,53 +1371,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129853122</v>
       </c>
       <c r="B8" t="n">
-        <v>92055</v>
+        <v>96393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572568</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587950</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,12 +1482,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1497,7 +1497,7 @@
         <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129850320</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129853667</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>129853671</v>
       </c>
       <c r="B16" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
+        <v>96393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96390</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,41 +3525,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B26" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3567,10 +3572,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R26" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3602,7 +3607,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3612,12 +3617,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3647,7 +3652,7 @@
         <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3763,62 +3768,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129880787</v>
+        <v>129881229</v>
       </c>
       <c r="B28" t="n">
-        <v>5469</v>
+        <v>91605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572432</v>
+        <v>572425</v>
       </c>
       <c r="R28" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3850,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,12 +3855,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,57 +3887,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881456</v>
+        <v>129880787</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>5469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101377</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572594</v>
+        <v>572432</v>
       </c>
       <c r="R29" t="n">
-        <v>6587833</v>
+        <v>6587788</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,41 +4248,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B32" t="n">
-        <v>91839</v>
+        <v>96393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4290,13 +4287,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R32" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4325,7 +4322,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4332,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4370,7 +4367,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4486,38 +4483,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129880315</v>
+        <v>129881407</v>
       </c>
       <c r="B34" t="n">
-        <v>96390</v>
+        <v>91842</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572590</v>
+        <v>572508</v>
       </c>
       <c r="R34" t="n">
-        <v>6587967</v>
+        <v>6587870</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>129880860</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129879675</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129880838</v>
       </c>
       <c r="B42" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97076</v>
+        <v>97079</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,41 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,55 +779,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,42 +1030,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>92058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R5" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,53 +1137,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129848578</v>
+        <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>92058</v>
+        <v>96393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572671</v>
+        <v>572568</v>
       </c>
       <c r="R6" t="n">
-        <v>6587913</v>
+        <v>6587950</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,53 +1248,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852516</v>
+        <v>129853663</v>
       </c>
       <c r="B7" t="n">
-        <v>92058</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1306,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572574</v>
+        <v>572512</v>
       </c>
       <c r="R7" t="n">
-        <v>6587839</v>
+        <v>6587864</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,50 +1363,53 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853122</v>
+        <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>96393</v>
+        <v>92058</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572568</v>
+        <v>572671</v>
       </c>
       <c r="R8" t="n">
-        <v>6587950</v>
+        <v>6587913</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,12 +1482,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96393</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>96393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>96393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96393</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,41 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,55 +779,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,41 +1030,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129853122</v>
       </c>
       <c r="B5" t="n">
-        <v>92058</v>
+        <v>96394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572568</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587950</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1129,54 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129853663</v>
       </c>
       <c r="B6" t="n">
-        <v>96393</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572512</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587864</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1223,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,42 +1256,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>92059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,12 +1363,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1378,7 +1378,7 @@
         <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,35 +1505,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,24 +1569,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1597,21 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,30 +1640,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,14 +1709,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,21 +1746,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3525,46 +3525,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881456</v>
+        <v>129881338</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>91606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3572,13 +3567,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572594</v>
+        <v>572461</v>
       </c>
       <c r="R26" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3607,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3617,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3649,10 +3644,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B27" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3691,13 +3686,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R27" t="n">
         <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3726,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3736,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,41 +3763,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B28" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,38 +4248,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129880315</v>
+        <v>129881108</v>
       </c>
       <c r="B32" t="n">
-        <v>96393</v>
+        <v>91606</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4287,13 +4290,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572590</v>
+        <v>572440</v>
       </c>
       <c r="R32" t="n">
-        <v>6587967</v>
+        <v>6587862</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4322,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4332,12 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4364,10 +4367,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881108</v>
+        <v>129881407</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
+        <v>91843</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4375,21 +4378,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4406,10 +4409,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572440</v>
+        <v>572508</v>
       </c>
       <c r="R33" t="n">
-        <v>6587862</v>
+        <v>6587870</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4451,12 +4454,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4483,41 +4486,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>91842</v>
+        <v>96394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R34" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97079</v>
+        <v>97080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853667</v>
+        <v>129849857</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,31 +2265,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,13 +2296,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572538</v>
+        <v>572655</v>
       </c>
       <c r="R15" t="n">
-        <v>6587829</v>
+        <v>6587890</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2341,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,76 +2356,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853671</v>
+        <v>129850334</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572561</v>
+        <v>572673</v>
       </c>
       <c r="R16" t="n">
-        <v>6587819</v>
+        <v>6587920</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2457,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,53 +2472,52 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853667</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2541,10 +2527,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572538</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587829</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2576,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2572,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129849857</v>
+        <v>129853671</v>
       </c>
       <c r="B18" t="n">
-        <v>91606</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,44 +2610,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572655</v>
+        <v>572561</v>
       </c>
       <c r="R18" t="n">
-        <v>6587890</v>
+        <v>6587819</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2695,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96394</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>96394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3763,57 +3763,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881456</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572594</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587833</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3845,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,62 +3892,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129880787</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>5469</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572432</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587788</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4248,41 +4248,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129881108</v>
+        <v>129880315</v>
       </c>
       <c r="B32" t="n">
-        <v>91606</v>
+        <v>96394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4290,13 +4287,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572440</v>
+        <v>572590</v>
       </c>
       <c r="R32" t="n">
-        <v>6587862</v>
+        <v>6587967</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4325,7 +4322,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4335,12 +4332,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Vidväxt på granlåga</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,10 +4364,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881407</v>
+        <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91843</v>
+        <v>91606</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4378,21 +4375,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4409,10 +4406,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572508</v>
+        <v>572440</v>
       </c>
       <c r="R33" t="n">
-        <v>6587870</v>
+        <v>6587862</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4444,7 +4441,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4454,12 +4451,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4486,38 +4483,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129880315</v>
+        <v>129881407</v>
       </c>
       <c r="B34" t="n">
-        <v>96394</v>
+        <v>91843</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572590</v>
+        <v>572508</v>
       </c>
       <c r="R34" t="n">
-        <v>6587967</v>
+        <v>6587870</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -1030,38 +1030,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129853122</v>
+        <v>129853663</v>
       </c>
       <c r="B5" t="n">
-        <v>96394</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572568</v>
+        <v>572512</v>
       </c>
       <c r="R5" t="n">
-        <v>6587950</v>
+        <v>6587864</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,42 +1145,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>92059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1184,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R6" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,53 +1252,50 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852516</v>
+        <v>129853122</v>
       </c>
       <c r="B7" t="n">
-        <v>92059</v>
+        <v>96394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572574</v>
+        <v>572568</v>
       </c>
       <c r="R7" t="n">
-        <v>6587839</v>
+        <v>6587950</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,12 +1363,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129849857</v>
+        <v>129853667</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,30 +2265,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2296,13 +2297,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572655</v>
+        <v>572538</v>
       </c>
       <c r="R15" t="n">
-        <v>6587890</v>
+        <v>6587829</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2331,7 +2332,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2341,7 +2342,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,69 +2357,76 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R16" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2455,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,7 +2465,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,52 +2485,53 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853667</v>
+        <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2527,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572538</v>
+        <v>572673</v>
       </c>
       <c r="R17" t="n">
-        <v>6587829</v>
+        <v>6587920</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2562,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2572,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,10 +2613,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853671</v>
+        <v>129849857</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>91606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,53 +2624,44 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572561</v>
+        <v>572655</v>
       </c>
       <c r="R18" t="n">
-        <v>6587819</v>
+        <v>6587890</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,12 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>96394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96394</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3763,62 +3763,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129880787</v>
+        <v>129881456</v>
       </c>
       <c r="B28" t="n">
-        <v>5469</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572432</v>
+        <v>572594</v>
       </c>
       <c r="R28" t="n">
-        <v>6587788</v>
+        <v>6587833</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3850,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,12 +3855,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,57 +3887,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881456</v>
+        <v>129880787</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>5469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>101377</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572594</v>
+        <v>572432</v>
       </c>
       <c r="R29" t="n">
-        <v>6587833</v>
+        <v>6587788</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91606</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,42 +1030,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129853663</v>
+        <v>129853122</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>96411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572512</v>
+        <v>572568</v>
       </c>
       <c r="R5" t="n">
-        <v>6587864</v>
+        <v>6587950</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129852516</v>
+        <v>129848578</v>
       </c>
       <c r="B6" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572574</v>
+        <v>572671</v>
       </c>
       <c r="R6" t="n">
-        <v>6587839</v>
+        <v>6587913</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,38 +1260,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853122</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>96394</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572568</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587950</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1347,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,53 +1367,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129853663</v>
       </c>
       <c r="B8" t="n">
-        <v>92059</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572512</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587864</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,30 +1505,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,14 +1574,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,21 +1611,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>91623</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,35 +1639,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,24 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,6 +1719,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,6 +1731,21 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
         <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853667</v>
+        <v>129849857</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>91623</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,31 +2265,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2297,13 +2296,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572538</v>
+        <v>572655</v>
       </c>
       <c r="R15" t="n">
-        <v>6587829</v>
+        <v>6587890</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2341,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,19 +2356,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853671</v>
+        <v>129853667</v>
       </c>
       <c r="B16" t="n">
         <v>57737</v>
@@ -2397,36 +2396,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572561</v>
+        <v>572538</v>
       </c>
       <c r="R16" t="n">
-        <v>6587819</v>
+        <v>6587829</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2485,69 +2471,76 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2579,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,53 +2599,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129849857</v>
+        <v>129850334</v>
       </c>
       <c r="B18" t="n">
-        <v>91606</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572655</v>
+        <v>572673</v>
       </c>
       <c r="R18" t="n">
-        <v>6587890</v>
+        <v>6587920</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3525,10 +3525,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B26" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R26" t="n">
         <v>6587873</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,10 +3644,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881229</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3686,13 +3686,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572425</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
         <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3731,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,57 +3763,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881456</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572594</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587833</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3845,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,62 +3892,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129880787</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>5469</v>
+        <v>98815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572432</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587788</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,38 +4248,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129880315</v>
+        <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>96394</v>
+        <v>91860</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4287,13 +4290,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572590</v>
+        <v>572508</v>
       </c>
       <c r="R32" t="n">
-        <v>6587967</v>
+        <v>6587870</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4322,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4332,12 +4335,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Kudde 30 cm hög</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4367,7 +4370,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4483,41 +4486,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129881407</v>
+        <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>91843</v>
+        <v>96411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1101</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572508</v>
+        <v>572590</v>
       </c>
       <c r="R34" t="n">
-        <v>6587870</v>
+        <v>6587967</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97080</v>
+        <v>97097</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>90988</v>
+        <v>91005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129848578</v>
       </c>
       <c r="B5" t="n">
         <v>92092</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572671</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587913</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,38 +1149,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129853663</v>
       </c>
       <c r="B6" t="n">
-        <v>96427</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572512</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587864</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,42 +1264,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>92092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1306,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1351,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,53 +1371,50 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129853122</v>
       </c>
       <c r="B8" t="n">
-        <v>92092</v>
+        <v>96427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572568</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587950</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>91639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,35 +1505,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,24 +1569,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1597,21 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>91639</v>
+        <v>57900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,30 +1640,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,14 +1709,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,21 +1746,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>96427</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96427</v>
+        <v>57738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,57 +3525,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881456</v>
+        <v>129880787</v>
       </c>
       <c r="B26" t="n">
-        <v>98831</v>
+        <v>5469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>101377</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572594</v>
+        <v>572432</v>
       </c>
       <c r="R26" t="n">
-        <v>6587833</v>
+        <v>6587788</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3607,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3617,12 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3649,41 +3654,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881229</v>
+        <v>129881456</v>
       </c>
       <c r="B27" t="n">
-        <v>91639</v>
+        <v>98831</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3691,10 +3701,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572425</v>
+        <v>572594</v>
       </c>
       <c r="R27" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3726,7 +3736,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3736,12 +3746,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,7 +3778,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B28" t="n">
         <v>91639</v>
@@ -3810,13 +3820,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R28" t="n">
         <v>6587873</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,7 +3855,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,12 +3865,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3887,65 +3897,55 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129880787</v>
+        <v>129881338</v>
       </c>
       <c r="B29" t="n">
-        <v>5469</v>
+        <v>91639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572432</v>
+        <v>572461</v>
       </c>
       <c r="R29" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,41 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,55 +779,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96427</v>
+        <v>57738</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>96427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129848578</v>
+        <v>129852516</v>
       </c>
       <c r="B5" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572671</v>
+        <v>572574</v>
       </c>
       <c r="R5" t="n">
-        <v>6587913</v>
+        <v>6587839</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,42 +1149,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853663</v>
+        <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>96429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1192,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572512</v>
+        <v>572568</v>
       </c>
       <c r="R6" t="n">
-        <v>6587864</v>
+        <v>6587950</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1227,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,41 +1260,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852516</v>
+        <v>129853663</v>
       </c>
       <c r="B7" t="n">
-        <v>92092</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1306,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572574</v>
+        <v>572512</v>
       </c>
       <c r="R7" t="n">
-        <v>6587839</v>
+        <v>6587864</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,50 +1363,53 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853122</v>
+        <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>96427</v>
+        <v>92094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572568</v>
+        <v>572671</v>
       </c>
       <c r="R8" t="n">
-        <v>6587950</v>
+        <v>6587913</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>91639</v>
+        <v>57900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,30 +1505,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,14 +1574,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,21 +1611,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>57900</v>
+        <v>91641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,35 +1639,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,24 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,6 +1719,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,6 +1731,21 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2254,40 +2254,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853667</v>
+        <v>129850334</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2297,10 +2298,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572538</v>
+        <v>572673</v>
       </c>
       <c r="R15" t="n">
-        <v>6587829</v>
+        <v>6587920</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2332,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2342,7 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,10 +2370,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129853671</v>
+        <v>129849857</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,53 +2381,44 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572561</v>
+        <v>572655</v>
       </c>
       <c r="R16" t="n">
-        <v>6587819</v>
+        <v>6587890</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2465,12 +2457,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,41 +2484,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853667</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2541,10 +2527,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572538</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587829</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2576,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2572,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129849857</v>
+        <v>129853671</v>
       </c>
       <c r="B18" t="n">
-        <v>91639</v>
+        <v>57738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2624,44 +2610,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572655</v>
+        <v>572561</v>
       </c>
       <c r="R18" t="n">
-        <v>6587890</v>
+        <v>6587819</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2695,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>96429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96427</v>
+        <v>57738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,62 +3525,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129880787</v>
+        <v>129881229</v>
       </c>
       <c r="B26" t="n">
-        <v>5469</v>
+        <v>91641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572432</v>
+        <v>572425</v>
       </c>
       <c r="R26" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3612,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3654,46 +3644,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881456</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>91641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3701,13 +3686,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572594</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
-        <v>6587833</v>
+        <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3736,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3746,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3778,52 +3763,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881229</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572425</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3865,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3897,41 +3892,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881338</v>
+        <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>98833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3939,13 +3939,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572461</v>
+        <v>572594</v>
       </c>
       <c r="R29" t="n">
-        <v>6587873</v>
+        <v>6587833</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>91876</v>
+        <v>91878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,41 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>5177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -717,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -762,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,55 +779,53 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +878,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,41 +1030,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129853122</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>96516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1072,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572568</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587950</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1129,53 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129848578</v>
       </c>
       <c r="B6" t="n">
-        <v>96429</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1188,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572671</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587913</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,54 +1248,53 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129852516</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572574</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587839</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1347,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,53 +1367,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129853663</v>
       </c>
       <c r="B8" t="n">
-        <v>92094</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1422,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572512</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587864</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,35 +1505,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1541,13 +1536,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,24 +1569,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,6 +1585,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1611,6 +1597,21 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>57985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1639,30 +1640,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,13 +1676,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,14 +1709,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1735,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1731,21 +1746,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
         <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2254,57 +2254,64 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129850334</v>
+        <v>129853671</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572673</v>
+        <v>572561</v>
       </c>
       <c r="R15" t="n">
-        <v>6587920</v>
+        <v>6587819</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2333,7 +2340,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2350,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,12 +2370,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2373,7 +2385,7 @@
         <v>129849857</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2484,40 +2496,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853667</v>
+        <v>129850334</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2527,10 +2540,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572538</v>
+        <v>572673</v>
       </c>
       <c r="R17" t="n">
-        <v>6587829</v>
+        <v>6587920</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2562,7 +2575,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2572,7 +2585,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2599,10 +2612,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853671</v>
+        <v>129853667</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,36 +2640,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572561</v>
+        <v>572538</v>
       </c>
       <c r="R18" t="n">
-        <v>6587819</v>
+        <v>6587829</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,12 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,38 +3183,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B23" t="n">
-        <v>96429</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3257,7 +3261,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,7 +3271,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,42 +3298,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>96516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,10 +3525,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881229</v>
+        <v>129881338</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572425</v>
+        <v>572461</v>
       </c>
       <c r="R26" t="n">
         <v>6587873</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,55 +3644,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881338</v>
+        <v>129880787</v>
       </c>
       <c r="B27" t="n">
-        <v>91641</v>
+        <v>5469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572461</v>
+        <v>572432</v>
       </c>
       <c r="R27" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3721,7 +3731,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3731,12 +3741,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,62 +3773,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129880787</v>
+        <v>129881229</v>
       </c>
       <c r="B28" t="n">
-        <v>5469</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572432</v>
+        <v>572425</v>
       </c>
       <c r="R28" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3895,7 +3895,7 @@
         <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>91878</v>
+        <v>91965</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129879675</v>
       </c>
       <c r="B40" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129880838</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>91641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R2" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,53 +782,55 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129849269</v>
+        <v>129852135</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572671</v>
+        <v>572573</v>
       </c>
       <c r="R3" t="n">
-        <v>6587913</v>
+        <v>6587903</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,12 +898,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1030,38 +1030,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129853122</v>
+        <v>129852516</v>
       </c>
       <c r="B5" t="n">
-        <v>96516</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572568</v>
+        <v>572574</v>
       </c>
       <c r="R5" t="n">
-        <v>6587950</v>
+        <v>6587839</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1117,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,53 +1137,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129848578</v>
+        <v>129853122</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>96429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1183,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572671</v>
+        <v>572568</v>
       </c>
       <c r="R6" t="n">
-        <v>6587913</v>
+        <v>6587950</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,53 +1248,54 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129852516</v>
+        <v>129853663</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1302,13 +1303,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572574</v>
+        <v>572512</v>
       </c>
       <c r="R7" t="n">
-        <v>6587839</v>
+        <v>6587864</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,54 +1363,53 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129853663</v>
+        <v>129848578</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>92094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1422,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572512</v>
+        <v>572671</v>
       </c>
       <c r="R8" t="n">
-        <v>6587864</v>
+        <v>6587913</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1457,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129861934</v>
+        <v>129863852</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>57900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,30 +1505,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1536,13 +1541,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572538</v>
       </c>
       <c r="R9" t="n">
-        <v>6587848</v>
+        <v>6587894</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,14 +1574,24 @@
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1600,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,21 +1611,6 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129863852</v>
+        <v>129861934</v>
       </c>
       <c r="B10" t="n">
-        <v>57985</v>
+        <v>91641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,35 +1639,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1676,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572538</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6587894</v>
+        <v>6587848</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,24 +1703,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,6 +1719,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1746,6 +1731,21 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
         <v>129847959</v>
       </c>
       <c r="B11" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>129853669</v>
       </c>
       <c r="B12" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2254,64 +2254,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129853671</v>
+        <v>129850334</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572561</v>
+        <v>572673</v>
       </c>
       <c r="R15" t="n">
-        <v>6587819</v>
+        <v>6587920</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2350,12 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,12 +2358,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2385,7 +2373,7 @@
         <v>129849857</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2496,41 +2484,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129850334</v>
+        <v>129853667</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2540,10 +2527,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572673</v>
+        <v>572538</v>
       </c>
       <c r="R17" t="n">
-        <v>6587920</v>
+        <v>6587829</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2575,7 +2562,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2585,7 +2572,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853667</v>
+        <v>129853671</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2640,28 +2627,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572538</v>
+        <v>572561</v>
       </c>
       <c r="R18" t="n">
-        <v>6587829</v>
+        <v>6587819</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2695,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,12 +2715,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
         <v>129850336</v>
       </c>
       <c r="B19" t="n">
-        <v>96516</v>
+        <v>96429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>129848066</v>
       </c>
       <c r="B20" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129852861</v>
       </c>
       <c r="B22" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3183,42 +3183,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850330</v>
+        <v>129850374</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>96429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3226,10 +3222,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572647</v>
+        <v>572599</v>
       </c>
       <c r="R23" t="n">
-        <v>6587994</v>
+        <v>6587880</v>
       </c>
       <c r="S23" t="n">
         <v>8</v>
@@ -3261,7 +3257,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3271,7 +3267,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,38 +3294,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850374</v>
+        <v>129850330</v>
       </c>
       <c r="B24" t="n">
-        <v>96516</v>
+        <v>57738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572599</v>
+        <v>572647</v>
       </c>
       <c r="R24" t="n">
-        <v>6587880</v>
+        <v>6587994</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,10 +3525,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881338</v>
+        <v>129881229</v>
       </c>
       <c r="B26" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572461</v>
+        <v>572425</v>
       </c>
       <c r="R26" t="n">
         <v>6587873</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,65 +3644,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129880787</v>
+        <v>129881338</v>
       </c>
       <c r="B27" t="n">
-        <v>5469</v>
+        <v>91641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572432</v>
+        <v>572461</v>
       </c>
       <c r="R27" t="n">
-        <v>6587788</v>
+        <v>6587873</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3731,7 +3721,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3741,12 +3731,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3773,52 +3763,62 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129881229</v>
+        <v>129880787</v>
       </c>
       <c r="B28" t="n">
-        <v>91728</v>
+        <v>5469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572425</v>
+        <v>572432</v>
       </c>
       <c r="R28" t="n">
-        <v>6587873</v>
+        <v>6587788</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3895,7 +3895,7 @@
         <v>129881456</v>
       </c>
       <c r="B29" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>129880591</v>
       </c>
       <c r="B30" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129879688</v>
       </c>
       <c r="B31" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>129881407</v>
       </c>
       <c r="B32" t="n">
-        <v>91965</v>
+        <v>91878</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>129881108</v>
       </c>
       <c r="B33" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>129880315</v>
       </c>
       <c r="B34" t="n">
-        <v>96516</v>
+        <v>96429</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>129878905</v>
       </c>
       <c r="B35" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129881042</v>
       </c>
       <c r="B36" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>129880273</v>
       </c>
       <c r="B38" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129879675</v>
       </c>
       <c r="B40" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>129880712</v>
       </c>
       <c r="B41" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>129880838</v>
       </c>
       <c r="B42" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>129881468</v>
       </c>
       <c r="B43" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129880557</v>
       </c>
       <c r="B45" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129880266</v>
       </c>
       <c r="B46" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>129881633</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>129880167</v>
       </c>
       <c r="B48" t="n">
-        <v>97202</v>
+        <v>97115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>129879841</v>
       </c>
       <c r="B49" t="n">
-        <v>91110</v>
+        <v>91023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129849269</v>
+        <v>129881407</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572671</v>
+        <v>572508</v>
       </c>
       <c r="R2" t="n">
-        <v>6587913</v>
+        <v>6587870</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,27 +747,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
+          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,43 +794,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129852135</v>
+        <v>129849269</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572573</v>
+        <v>572671</v>
       </c>
       <c r="R3" t="n">
-        <v>6587903</v>
+        <v>6587913</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer resupinat på granlåga tillsammans med rynkskinn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,59 +901,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129848357</v>
+        <v>129849857</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,13 +955,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572691</v>
+        <v>572655</v>
       </c>
       <c r="R4" t="n">
-        <v>6587977</v>
+        <v>6587890</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,40 +1027,36 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129852516</v>
+        <v>129853669</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1072,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572574</v>
+        <v>572538</v>
       </c>
       <c r="R5" t="n">
-        <v>6587839</v>
+        <v>6587829</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1117,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,64 +1125,67 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129853122</v>
+        <v>129861934</v>
       </c>
       <c r="B6" t="n">
-        <v>96429</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572568</v>
+        <v>572577</v>
       </c>
       <c r="R6" t="n">
-        <v>6587950</v>
+        <v>6587848</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,19 +1212,14 @@
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:18</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer ca 3 meter på granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,28 +1228,54 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129853663</v>
+        <v>129880273</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,31 +1283,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1314,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572512</v>
+        <v>572598</v>
       </c>
       <c r="R7" t="n">
-        <v>6587864</v>
+        <v>6587998</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1344,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på granlåga i sumpskogsmiljö</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,44 +1379,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129848578</v>
+        <v>129881042</v>
       </c>
       <c r="B8" t="n">
-        <v>92094</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572671</v>
+        <v>572434</v>
       </c>
       <c r="R8" t="n">
-        <v>6587913</v>
+        <v>6587846</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1447,27 +1463,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer ca 3 m på undersida av granlåga</t>
+          <t>Växer på granlåga i blockrik terräng vid hällmark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129863852</v>
+        <v>129881108</v>
       </c>
       <c r="B9" t="n">
-        <v>57900</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,46 +1521,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572538</v>
+        <v>572440</v>
       </c>
       <c r="R9" t="n">
-        <v>6587894</v>
+        <v>6587862</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1571,27 +1582,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
+          <t>Vidväxt på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,16 +1613,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1628,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129861934</v>
+        <v>129881229</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,17 +1667,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572425</v>
       </c>
       <c r="R10" t="n">
-        <v>6587848</v>
+        <v>6587873</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,17 +1701,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer ca 3 meter på granlåga.</t>
+          <t>Flertalet granlågor i området med vidväxt ullticka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,34 +1730,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1763,57 +1748,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129847959</v>
+        <v>129881338</v>
       </c>
       <c r="B11" t="n">
-        <v>58113</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572722</v>
+        <v>572461</v>
       </c>
       <c r="R11" t="n">
-        <v>6588063</v>
+        <v>6587873</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1840,22 +1820,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129853669</v>
+        <v>129848578</v>
       </c>
       <c r="B12" t="n">
-        <v>91641</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,25 +1878,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1920,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572538</v>
+        <v>572671</v>
       </c>
       <c r="R12" t="n">
-        <v>6587829</v>
+        <v>6587913</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1954,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer ca 3 m på undersida av granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,73 +1974,67 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129861976</v>
+        <v>129852516</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karlsro, Broby Sofieberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572626</v>
+        <v>572574</v>
       </c>
       <c r="R13" t="n">
-        <v>6587871</v>
+        <v>6587839</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2075,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2085,7 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer på grov granlåga i äldre barrblandskog. Skogen är avverkningsanmäld och ingen avgränsning eller hänsyn tagen till lågan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,34 +2087,8 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2138,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129850320</v>
+        <v>129850336</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,46 +2116,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572693</v>
+        <v>572660</v>
       </c>
       <c r="R14" t="n">
-        <v>6588000</v>
+        <v>6587856</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2217,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2227,7 +2189,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,10 +2216,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129850334</v>
+        <v>129850374</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,32 +2227,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2298,10 +2255,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572673</v>
+        <v>572599</v>
       </c>
       <c r="R15" t="n">
-        <v>6587920</v>
+        <v>6587880</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2333,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,41 +2327,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129849857</v>
+        <v>129853122</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2412,13 +2366,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572655</v>
+        <v>572568</v>
       </c>
       <c r="R16" t="n">
-        <v>6587890</v>
+        <v>6587950</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,7 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,54 +2426,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129853667</v>
+        <v>129880315</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2527,13 +2477,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572538</v>
+        <v>572590</v>
       </c>
       <c r="R17" t="n">
-        <v>6587829</v>
+        <v>6587967</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2557,22 +2507,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kudde 30 cm hög</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,76 +2542,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129853671</v>
+        <v>129878905</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>97394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572561</v>
+        <v>572680</v>
       </c>
       <c r="R18" t="n">
-        <v>6587819</v>
+        <v>6588009</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2680,27 +2623,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flög över skogen. Gott om färska hackmärken.</t>
+          <t>Växer på rötad tallåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129850336</v>
+        <v>129879688</v>
       </c>
       <c r="B19" t="n">
-        <v>96429</v>
+        <v>97394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2738,21 +2681,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2766,13 +2709,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572660</v>
+        <v>572642</v>
       </c>
       <c r="R19" t="n">
-        <v>6587856</v>
+        <v>6587983</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2796,22 +2739,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2826,49 +2774,50 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129848066</v>
+        <v>129880167</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>97394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2876,13 +2825,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572716</v>
+        <v>572644</v>
       </c>
       <c r="R20" t="n">
-        <v>6588058</v>
+        <v>6588032</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2906,22 +2855,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Växer på tallåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,22 +2890,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129853662</v>
+        <v>129880266</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>97394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,46 +2913,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572512</v>
+        <v>572635</v>
       </c>
       <c r="R21" t="n">
-        <v>6587864</v>
+        <v>6588012</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3022,22 +2971,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer grov rötad tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3052,56 +3006,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129852861</v>
+        <v>129880557</v>
       </c>
       <c r="B22" t="n">
-        <v>98833</v>
+        <v>97394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3111,13 +3057,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572560</v>
+        <v>572578</v>
       </c>
       <c r="R22" t="n">
-        <v>6587918</v>
+        <v>6587934</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3141,22 +3087,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i fuktig skogsmiljö</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,22 +3122,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129850374</v>
+        <v>129880591</v>
       </c>
       <c r="B23" t="n">
-        <v>96429</v>
+        <v>97394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3194,21 +3145,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>2590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3222,13 +3173,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>572599</v>
+        <v>572591</v>
       </c>
       <c r="R23" t="n">
-        <v>6587880</v>
+        <v>6587910</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3252,22 +3203,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stor förekomst på tallåga i sumpig skogsmiljö</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3282,68 +3238,67 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129850330</v>
+        <v>129879841</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>91282</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572647</v>
+        <v>572640</v>
       </c>
       <c r="R24" t="n">
-        <v>6587994</v>
+        <v>6588022</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3367,22 +3322,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer på tallåga i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,22 +3357,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129848027</v>
+        <v>129850330</v>
       </c>
       <c r="B25" t="n">
-        <v>5177</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3420,46 +3380,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572720</v>
+        <v>572647</v>
       </c>
       <c r="R25" t="n">
-        <v>6588056</v>
+        <v>6587994</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3488,7 +3447,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3498,7 +3457,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3525,41 +3484,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129881229</v>
+        <v>129853663</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3567,13 +3527,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572425</v>
+        <v>572512</v>
       </c>
       <c r="R26" t="n">
-        <v>6587873</v>
+        <v>6587864</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3597,27 +3557,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Flertalet granlågor i området med vidväxt ullticka</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3632,53 +3587,54 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129881338</v>
+        <v>129853667</v>
       </c>
       <c r="B27" t="n">
-        <v>91641</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3686,13 +3642,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572461</v>
+        <v>572538</v>
       </c>
       <c r="R27" t="n">
-        <v>6587873</v>
+        <v>6587829</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3716,27 +3672,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Växer på gammal granlåga i fuktig skogsmiljö</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3751,22 +3702,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129880787</v>
+        <v>129853671</v>
       </c>
       <c r="B28" t="n">
-        <v>5469</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3774,21 +3725,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3796,12 +3747,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3815,13 +3765,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572432</v>
+        <v>572561</v>
       </c>
       <c r="R28" t="n">
-        <v>6587788</v>
+        <v>6587819</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3845,27 +3795,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Kläckhål i björklåga</t>
+          <t>Flög över skogen. Gott om färska hackmärken.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,57 +3842,61 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129881456</v>
+        <v>129879675</v>
       </c>
       <c r="B29" t="n">
-        <v>98833</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572594</v>
+        <v>572661</v>
       </c>
       <c r="R29" t="n">
-        <v>6587833</v>
+        <v>6588006</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3974,7 +3928,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3984,12 +3938,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Växer i sluttning ner mot mosse.</t>
+          <t>Färska hackmärken på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4016,10 +3970,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129880591</v>
+        <v>129880838</v>
       </c>
       <c r="B30" t="n">
-        <v>97115</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4027,41 +3981,53 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>572591</v>
+        <v>572431</v>
       </c>
       <c r="R30" t="n">
-        <v>6587910</v>
+        <v>6587805</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4090,7 +4056,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4100,12 +4066,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Stor förekomst på tallåga i sumpig skogsmiljö</t>
+          <t>Färska hackmärken på tall i hällmarksskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4132,10 +4098,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129879688</v>
+        <v>129852135</v>
       </c>
       <c r="B31" t="n">
-        <v>97115</v>
+        <v>5179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4143,27 +4109,32 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4171,13 +4142,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>572642</v>
+        <v>572573</v>
       </c>
       <c r="R31" t="n">
-        <v>6587983</v>
+        <v>6587903</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4201,27 +4172,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer på tallåga i äldre barrblandskog.</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4236,53 +4202,55 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129881407</v>
+        <v>129853662</v>
       </c>
       <c r="B32" t="n">
-        <v>91878</v>
+        <v>5179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1101</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4290,13 +4258,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>572508</v>
+        <v>572512</v>
       </c>
       <c r="R32" t="n">
-        <v>6587870</v>
+        <v>6587864</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4320,27 +4288,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer på rotdelen av granlåga i fuktig äldre barrblandskog</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4355,67 +4318,73 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129881108</v>
+        <v>129861976</v>
       </c>
       <c r="B33" t="n">
-        <v>91641</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>572440</v>
+        <v>572626</v>
       </c>
       <c r="R33" t="n">
-        <v>6587862</v>
+        <v>6587871</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4439,27 +4408,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Vidväxt på granlåga</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4468,8 +4432,34 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4486,10 +4476,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129880315</v>
+        <v>129880352</v>
       </c>
       <c r="B34" t="n">
-        <v>96429</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4497,41 +4487,54 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572590</v>
+        <v>572564</v>
       </c>
       <c r="R34" t="n">
-        <v>6587967</v>
+        <v>6587969</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4560,7 +4563,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4570,12 +4573,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Kudde 30 cm hög</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4602,10 +4600,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129878905</v>
+        <v>129880914</v>
       </c>
       <c r="B35" t="n">
-        <v>97115</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,41 +4611,54 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572680</v>
+        <v>572386</v>
       </c>
       <c r="R35" t="n">
-        <v>6588009</v>
+        <v>6587825</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4686,12 +4697,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer på rötad tallåga</t>
+          <t>På gran I hällmarksskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4718,52 +4729,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129881042</v>
+        <v>129881486</v>
       </c>
       <c r="B36" t="n">
-        <v>91641</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>572434</v>
+        <v>572603</v>
       </c>
       <c r="R36" t="n">
-        <v>6587846</v>
+        <v>6587829</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4795,7 +4816,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4805,12 +4826,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer på granlåga i blockrik terräng vid hällmark</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4837,10 +4853,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129880860</v>
+        <v>129880787</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>5471</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4848,21 +4864,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>101377</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4889,13 +4905,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>572415</v>
+        <v>572432</v>
       </c>
       <c r="R37" t="n">
-        <v>6587791</v>
+        <v>6587788</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4924,7 +4940,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4934,12 +4950,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gnagspår på gammal tall i hällmarksskog</t>
+          <t>Kläckhål i björklåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,41 +4982,47 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129880273</v>
+        <v>129880927</v>
       </c>
       <c r="B38" t="n">
-        <v>91641</v>
+        <v>5471</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5008,13 +5030,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572598</v>
+        <v>572379</v>
       </c>
       <c r="R38" t="n">
-        <v>6587998</v>
+        <v>6587824</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5043,7 +5065,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5053,12 +5075,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer på granlåga i sumpskogsmiljö</t>
+          <t>På björkstubbe i hällmarksskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5085,32 +5107,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129881486</v>
+        <v>129863852</v>
       </c>
       <c r="B39" t="n">
-        <v>5177</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5118,29 +5140,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Karlsro, Broby Sofieberg, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572603</v>
+        <v>572538</v>
       </c>
       <c r="R39" t="n">
-        <v>6587829</v>
+        <v>6587894</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5167,22 +5184,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Talltita i avverkningsanmäld äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5193,6 +5215,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5209,10 +5241,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129879675</v>
+        <v>129880712</v>
       </c>
       <c r="B40" t="n">
-        <v>57738</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5220,21 +5252,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5246,7 +5278,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5256,17 +5288,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>572661</v>
+        <v>572458</v>
       </c>
       <c r="R40" t="n">
-        <v>6588006</v>
+        <v>6587778</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,7 +5327,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,12 +5337,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på tall</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5337,32 +5364,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129880712</v>
+        <v>129848357</v>
       </c>
       <c r="B41" t="n">
-        <v>57900</v>
+        <v>8455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5370,31 +5397,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>572458</v>
+        <v>572691</v>
       </c>
       <c r="R41" t="n">
-        <v>6587778</v>
+        <v>6587977</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5418,22 +5442,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5460,64 +5484,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129880838</v>
+        <v>129850320</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>8455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Karlsro, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572431</v>
+        <v>572693</v>
       </c>
       <c r="R42" t="n">
-        <v>6587805</v>
+        <v>6588000</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5541,27 +5558,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på tall i hällmarksskog</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5576,58 +5588,55 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129881468</v>
+        <v>129850334</v>
       </c>
       <c r="B43" t="n">
-        <v>98833</v>
+        <v>8455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5635,10 +5644,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572602</v>
+        <v>572673</v>
       </c>
       <c r="R43" t="n">
-        <v>6587826</v>
+        <v>6587920</v>
       </c>
       <c r="S43" t="n">
         <v>8</v>
@@ -5665,27 +5674,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Växer i mossan bland grov gran nära en mosse</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5700,22 +5704,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129880352</v>
+        <v>129880860</v>
       </c>
       <c r="B44" t="n">
-        <v>5177</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5723,21 +5727,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5764,13 +5768,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572564</v>
+        <v>572415</v>
       </c>
       <c r="R44" t="n">
-        <v>6587969</v>
+        <v>6587791</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5799,7 +5803,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5809,7 +5813,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Gnagspår på gammal tall i hällmarksskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5836,36 +5845,44 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129880557</v>
+        <v>129852861</v>
       </c>
       <c r="B45" t="n">
-        <v>97115</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5875,13 +5892,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572578</v>
+        <v>572560</v>
       </c>
       <c r="R45" t="n">
-        <v>6587934</v>
+        <v>6587918</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5905,27 +5922,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Växer på tallåga i fuktig skogsmiljö</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5940,61 +5952,69 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129880266</v>
+        <v>129881456</v>
       </c>
       <c r="B46" t="n">
-        <v>97202</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Karlsro, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572635</v>
+        <v>572594</v>
       </c>
       <c r="R46" t="n">
-        <v>6588012</v>
+        <v>6587833</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6026,7 +6046,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6036,12 +6056,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer grov rötad tallåga</t>
+          <t>Växer i sluttning ner mot mosse.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6068,10 +6088,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129881633</v>
+        <v>129881468</v>
       </c>
       <c r="B47" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6098,7 +6118,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6115,13 +6135,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572736</v>
+        <v>572602</v>
       </c>
       <c r="R47" t="n">
-        <v>6587886</v>
+        <v>6587826</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6150,7 +6170,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6160,12 +6180,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Över hundra plantor på ett stenblock. Mossrik och  Fuktig skogsmiljö</t>
+          <t>Växer i mossan bland grov gran nära en mosse</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6185,45 +6205,44 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Via Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129880167</v>
+        <v>129848066</v>
       </c>
       <c r="B48" t="n">
-        <v>97202</v>
+        <v>91909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6231,13 +6250,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572644</v>
+        <v>572716</v>
       </c>
       <c r="R48" t="n">
-        <v>6588032</v>
+        <v>6588058</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6261,27 +6280,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer på tallåga</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6296,22 +6310,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129879841</v>
+        <v>129848027</v>
       </c>
       <c r="B49" t="n">
-        <v>91110</v>
+        <v>5179</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6319,30 +6333,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5685</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6350,13 +6366,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572640</v>
+        <v>572720</v>
       </c>
       <c r="R49" t="n">
-        <v>6588022</v>
+        <v>6588056</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6380,27 +6396,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Växer på tallåga i äldre barrblandskog</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6415,15 +6426,502 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129847959</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>572722</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6588063</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129878825</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>572767</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6588027</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129881633</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>572736</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6587886</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Över hundra plantor på ett stenblock. Mossrik och  Fuktig skogsmiljö</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Via Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129881711</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Karlsro, Srm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>572742</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6587917</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tumbo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Växer nedanför ett berg två meter från Mellanskogs avgränsning och inom avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50944-2025 artfynd.xlsx
+++ b/artfynd/A 50944-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129849269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129849857</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853669</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129861934</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1498,6 +1533,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880273</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1617,6 +1657,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881042</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881108</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881229</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1974,6 +2029,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881338</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2093,6 +2153,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848578</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2212,6 +2277,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129852516</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850336</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2434,6 +2509,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850374</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2545,6 +2625,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853122</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2661,6 +2746,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880315</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2777,6 +2867,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129878905</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2893,6 +2988,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129879688</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3009,6 +3109,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880167</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3125,6 +3230,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880266</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3241,6 +3351,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880591</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3476,6 +3596,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129879841</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3591,6 +3716,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850330</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3706,6 +3836,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853663</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3821,6 +3956,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853667</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3949,6 +4089,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853671</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4077,6 +4222,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129879675</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4205,6 +4355,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880838</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4321,6 +4476,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848027</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4437,6 +4597,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129852135</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4553,6 +4718,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129853662</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4699,6 +4869,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129861976</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4823,6 +4998,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880352</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4952,6 +5132,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880914</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5076,6 +5261,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881486</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5205,6 +5395,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880787</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5330,6 +5525,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880927</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5449,6 +5649,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129847959</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5583,6 +5788,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129863852</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5706,6 +5916,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880712</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5826,6 +6041,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129878825</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5946,6 +6166,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848357</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6062,6 +6287,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850320</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6178,6 +6408,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850334</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6307,6 +6542,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129880860</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6426,6 +6666,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129852861</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6550,6 +6795,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881456</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6674,6 +6924,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881468</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6798,6 +7053,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881633</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6922,8 +7182,67 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129881711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>